--- a/Infection/Assets/ExcelData/SynthesisData/SynthesisUnitStatsData.xlsx
+++ b/Infection/Assets/ExcelData/SynthesisData/SynthesisUnitStatsData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Infection\Infection\Assets\ExcelData\SynthesisData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F09164-806C-4266-8571-5D11156C5E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375150AB-C95D-4C7A-8FEB-E3E80E01405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="645" yWindow="3615" windowWidth="26715" windowHeight="11295" xr2:uid="{24952D1D-5CB1-407C-A628-C41DADFF17DC}"/>
+    <workbookView xWindow="1080" yWindow="4185" windowWidth="26715" windowHeight="11295" xr2:uid="{24952D1D-5CB1-407C-A628-C41DADFF17DC}"/>
   </bookViews>
   <sheets>
     <sheet name="SynthesisUnitParameter" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>unitCode</t>
     <phoneticPr fontId="1"/>
@@ -105,6 +105,21 @@
       <t>カイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maxHp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>combo1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>combo2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tank</t>
   </si>
 </sst>
 </file>
@@ -468,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F6E53F-818E-4D42-ACCE-8948EA339D83}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -478,7 +493,7 @@
     <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,31 +501,40 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>20001</v>
       </c>
@@ -520,29 +544,38 @@
       <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2">
         <v>100</v>
       </c>
-      <c r="E2">
+      <c r="G2">
+        <v>200</v>
+      </c>
+      <c r="H2">
         <v>50</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>20</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>15</v>
       </c>
-      <c r="I2" t="b">
+      <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>20002</v>
       </c>
@@ -550,31 +583,40 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>200</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>350</v>
+      </c>
+      <c r="H3">
         <v>20</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>14</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>8</v>
       </c>
-      <c r="I3" t="b">
+      <c r="L3" t="b">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>20003</v>
       </c>
@@ -584,32 +626,41 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
         <v>150</v>
       </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>8</v>
-      </c>
       <c r="G4">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="H4">
         <v>10</v>
       </c>
-      <c r="I4" t="b">
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>4</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4" t="b">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C4" xr:uid="{97145AE8-83AB-43C8-BA99-9BB647EBDEB1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E4" xr:uid="{97145AE8-83AB-43C8-BA99-9BB647EBDEB1}">
       <formula1>"Attacker,Tank,Healer,Baffer,Debuffer,Archer,Wizard"</formula1>
     </dataValidation>
   </dataValidations>
